--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D854560-497F-4556-8A79-F8CE78517E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E3B7C1-AA58-4295-B0F2-DFE2E6F7C7D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="10" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>GranteePOCContact__c</t>
   </si>
   <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>DropDown</t>
   </si>
   <si>
@@ -362,13 +359,16 @@
   </si>
   <si>
     <t xml:space="preserve">Program </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{users:Automation_SPI} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,6 +387,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -409,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -419,6 +426,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -734,13 +744,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -759,10 +769,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -770,18 +780,18 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -792,13 +802,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,323 +819,323 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>54</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>68</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
         <v>23</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
         <v>24</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
         <v>25</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1136,14 +1146,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,106 +1164,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1265,13 +1275,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1290,47 +1300,48 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,48 +1352,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" t="s">
         <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1394,12 +1405,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1407,48 +1418,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1459,39 +1470,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1502,14 +1513,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,81 +1531,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>103</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>104</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>105</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1606,13 +1617,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1623,70 +1634,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>103</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>104</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
       <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1697,13 +1708,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1714,70 +1725,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>105</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>106</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>107</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1788,7 +1799,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E3B7C1-AA58-4295-B0F2-DFE2E6F7C7D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76177BE4-BB84-4180-96C2-23E4620B3B3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="10" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="9" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -361,14 +361,14 @@
     <t xml:space="preserve">Program </t>
   </si>
   <si>
-    <t xml:space="preserve">{users:Automation_SPI} </t>
+    <t>Debra Clements</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,13 +387,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FF297BDE"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -416,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -426,9 +419,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1310,7 +1300,7 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>108</v>
       </c>
     </row>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76177BE4-BB84-4180-96C2-23E4620B3B3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B6D77C-2E9E-48E7-B551-300C3872C7D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="9" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -362,13 +362,16 @@
   </si>
   <si>
     <t>Debra Clements</t>
+  </si>
+  <si>
+    <t>SPI Automation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,6 +391,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -406,10 +424,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -419,8 +438,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -769,8 +790,8 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>108</v>
+      <c r="C3" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -785,7 +806,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" tooltip="SPI Automation" display="https://lsc--qa--c.visualforce.com/0030r00000KHDtmAAH" xr:uid="{9473BE9D-04D1-45EE-93C8-87F02EE4FDE6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA479C98-91C2-411F-8124-A03BB6FCB803}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1FAE92-593B-4C58-B818-8645CBD6C3C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Automation Runtime Award Site Visit"</t>
+  </si>
+  <si>
+    <t>Automation SPI2</t>
   </si>
 </sst>
 </file>
@@ -744,13 +747,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -772,7 +775,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -780,10 +783,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -803,13 +806,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -820,7 +823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -831,7 +834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -842,7 +845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -853,7 +856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -864,7 +867,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -875,7 +878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -886,7 +889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -897,7 +900,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -908,7 +911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -919,7 +922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -930,7 +933,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -941,7 +944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -952,7 +955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -963,7 +966,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -974,7 +977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -985,7 +988,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -996,7 +999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1029,7 +1032,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1040,7 +1043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1062,7 +1065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1084,7 +1087,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1106,7 +1109,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1147,14 +1150,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1209,7 +1212,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1245,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1276,13 +1279,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1335,14 +1338,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1406,12 +1409,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1443,22 +1446,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1471,9 +1474,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1514,14 +1517,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1618,13 +1621,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1657,7 +1660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1679,7 +1682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1709,13 +1712,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1726,7 +1729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1737,7 +1740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1759,7 +1762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1770,7 +1773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1800,7 +1803,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1FAE92-593B-4C58-B818-8645CBD6C3C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94654E5F-9F4A-40A6-98A7-72C63B64B39B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="115">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -365,6 +365,21 @@
   </si>
   <si>
     <t>Automation SPI2</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldGranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>fieldMonitoringType__c</t>
+  </si>
+  <si>
+    <t>fieldVisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>fieldVisitEndDateTime__c</t>
   </si>
 </sst>
 </file>
@@ -769,7 +784,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>108</v>
@@ -780,7 +795,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
         <v>109</v>
@@ -791,7 +806,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -1540,7 +1555,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1551,7 +1566,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>20</v>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9C0062-D4E0-485E-A371-22E5133E5008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F580A7-D9D4-439D-9FCD-0F5ED5348C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="9" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="118">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -368,6 +368,27 @@
   </si>
   <si>
     <t>fieldVisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>VisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>VisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Pointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>SiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>SourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>SupportingCommentsQuestion1__c</t>
   </si>
 </sst>
 </file>
@@ -757,13 +778,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -785,7 +806,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -796,7 +817,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,13 +837,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -844,7 +865,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -855,7 +876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -866,7 +887,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -877,7 +898,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -888,7 +909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -899,7 +920,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -910,7 +931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -921,7 +942,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -932,7 +953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -943,7 +964,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -954,7 +975,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -965,7 +986,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -976,7 +997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -987,7 +1008,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -998,7 +1019,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1052,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1063,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1074,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1085,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1096,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1107,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1118,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1108,7 +1129,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1140,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1130,7 +1151,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1162,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1160,14 +1181,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1210,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1221,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1232,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1243,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1254,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1265,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1276,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1287,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1298,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1289,13 +1310,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1338,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1348,14 +1369,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1377,7 +1398,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1388,7 +1409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1420,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1419,12 +1440,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1440,7 +1461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1469,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1456,22 +1477,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1484,9 +1505,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,14 +1548,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,78 +1566,78 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -1631,13 +1652,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1659,7 +1680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1670,7 +1691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1681,7 +1702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1692,7 +1713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1703,7 +1724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1722,13 +1743,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,7 +1760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1750,7 +1771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1761,7 +1782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1772,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1783,7 +1804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1794,7 +1815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1813,7 +1834,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F580A7-D9D4-439D-9FCD-0F5ED5348C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263A4D9-CFF2-4369-85F8-1EC92B8CCA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="9" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -337,21 +337,6 @@
     <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
   </si>
   <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldPointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitPurpose__c</t>
-  </si>
-  <si>
-    <t>fieldSourceSiteVisit__c</t>
-  </si>
-  <si>
-    <t>fieldSupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
     <t xml:space="preserve">Program </t>
   </si>
   <si>
@@ -362,12 +347,6 @@
   </si>
   <si>
     <t>Automation Runtime Site Visit</t>
-  </si>
-  <si>
-    <t>fieldVisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>fieldVisitEndDateTime__c</t>
   </si>
   <si>
     <t>VisitDateandTime__c</t>
@@ -481,9 +460,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -521,7 +500,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -627,7 +606,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -769,7 +748,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -778,13 +757,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -803,10 +782,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -814,10 +793,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -837,13 +816,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -865,7 +844,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -876,7 +855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -887,7 +866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -898,7 +877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -909,7 +888,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -920,7 +899,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -931,7 +910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -942,7 +921,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -953,7 +932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -964,7 +943,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -975,7 +954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -986,7 +965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -997,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +987,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1019,7 +998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1030,7 +1009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1041,7 +1020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1052,7 +1031,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1063,7 +1042,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1074,7 +1053,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1085,7 +1064,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1075,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1097,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1140,7 +1119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1151,7 +1130,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1162,7 +1141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1181,14 +1160,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1210,7 +1189,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1221,7 +1200,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1232,7 +1211,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1243,7 +1222,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1254,7 +1233,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1265,7 +1244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1276,7 +1255,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1287,7 +1266,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1298,7 +1277,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1310,13 +1289,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1327,7 +1306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1335,10 +1314,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1349,7 +1328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1357,7 +1336,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1369,14 +1348,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1398,7 +1377,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1409,7 +1388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1420,7 +1399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1440,12 +1419,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1461,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1469,7 +1448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1477,22 +1456,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1505,9 +1484,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1518,7 +1497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1529,7 +1508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1548,14 +1527,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1566,78 +1545,78 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -1652,13 +1631,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1669,67 +1648,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1743,13 +1722,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1760,67 +1739,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1834,7 +1813,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9C0062-D4E0-485E-A371-22E5133E5008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7591A103-DEDF-48D6-8168-B282A69F2A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="114">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -358,23 +358,32 @@
     <t>Automation Runtime Award Site Visit"</t>
   </si>
   <si>
-    <t>Automation SPI3</t>
-  </si>
-  <si>
-    <t>Automation Runtime Site Visit</t>
-  </si>
-  <si>
     <t>fieldVisitDateandTime__c</t>
   </si>
   <si>
     <t>fieldVisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Department of Health</t>
+  </si>
+  <si>
+    <t>Victoria Leeds</t>
+  </si>
+  <si>
+    <t>Departmental description</t>
+  </si>
+  <si>
+    <t>At the request of the subrecipient</t>
+  </si>
+  <si>
+    <t>Through Project Based Learning, students acquire real world skills, achieve academic success, and find purpose</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +416,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -428,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -442,6 +457,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,9 +478,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +518,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -606,7 +624,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -748,7 +766,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -757,13 +775,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -782,21 +800,21 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,13 +834,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -844,7 +862,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -855,7 +873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -866,7 +884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -877,7 +895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -888,7 +906,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -899,7 +917,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -910,7 +928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -921,7 +939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -932,7 +950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -943,7 +961,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -954,7 +972,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -965,7 +983,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -976,7 +994,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -987,7 +1005,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -998,7 +1016,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1027,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1049,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1071,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1082,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1093,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1104,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1115,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1108,7 +1126,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1137,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1130,7 +1148,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1159,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1160,14 +1178,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="115.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1207,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1218,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1229,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1240,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1251,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1262,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1273,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1284,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1295,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1289,13 +1307,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1324,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1335,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1348,14 +1366,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1377,7 +1395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1388,7 +1406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1419,12 +1437,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1466,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1456,22 +1474,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1484,9 +1502,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1526,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,14 +1545,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,29 +1563,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1575,10 +1593,10 @@
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1586,10 +1604,10 @@
         <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1600,7 +1618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1611,7 +1629,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1619,7 +1637,7 @@
         <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1631,13 +1649,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,29 +1666,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1681,7 +1699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1692,7 +1710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1703,7 +1721,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1722,13 +1740,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,29 +1757,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1772,7 +1790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1783,7 +1801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1794,7 +1812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1813,7 +1831,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationProjects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263A4D9-CFF2-4369-85F8-1EC92B8CCA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -373,7 +372,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -755,11 +754,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -814,7 +813,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1158,7 +1157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1287,7 +1286,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1346,7 +1345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1417,7 +1416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1482,7 +1481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1525,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1629,7 +1628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1720,7 +1719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1811,7 +1810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263A4D9-CFF2-4369-85F8-1EC92B8CCA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802AE61-6947-4858-BB70-1B85AC960A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="10" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="114">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -346,9 +346,6 @@
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>Automation Runtime Site Visit</t>
-  </si>
-  <si>
     <t>VisitDateandTime__c</t>
   </si>
   <si>
@@ -368,6 +365,18 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Department of Health</t>
+  </si>
+  <si>
+    <t>Departmental description</t>
+  </si>
+  <si>
+    <t>Through Project Based Learning, students acquire real world skills, achieve academic success, and find purpose</t>
+  </si>
+  <si>
+    <t>At the request of the subrecipient</t>
   </si>
 </sst>
 </file>
@@ -428,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -442,6 +451,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,24 +769,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -782,10 +794,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -796,7 +808,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,13 +828,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -844,7 +856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -855,7 +867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -866,7 +878,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -877,7 +889,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -888,7 +900,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -899,7 +911,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -910,7 +922,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -921,7 +933,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -932,7 +944,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -943,7 +955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -954,7 +966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -965,7 +977,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -976,7 +988,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -987,7 +999,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -998,7 +1010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1032,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1043,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1054,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1065,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1076,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1109,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1108,7 +1120,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1131,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1130,7 +1142,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1153,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1160,14 +1172,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1201,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1212,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1223,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1234,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1245,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1256,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1267,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1278,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1289,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1289,13 +1301,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1329,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1348,14 +1360,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1377,7 +1389,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1388,7 +1400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1419,12 +1431,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1440,7 +1452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1456,22 +1468,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1484,9 +1496,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,99 +1539,99 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="C2" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3">
+        <v>104</v>
+      </c>
+      <c r="C3" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1631,13 +1643,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,67 +1660,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1722,13 +1734,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,67 +1751,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1813,7 +1825,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263A4D9-CFF2-4369-85F8-1EC92B8CCA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04E35FF-0AEE-49B9-8C48-2A58FB9CFEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -343,9 +343,6 @@
     <t>Automation Runtime Award Site Visit"</t>
   </si>
   <si>
-    <t>Automation SPI3</t>
-  </si>
-  <si>
     <t>Automation Runtime Site Visit</t>
   </si>
   <si>
@@ -368,6 +365,9 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Deshka Kostova</t>
   </si>
 </sst>
 </file>
@@ -757,13 +757,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -782,10 +782,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -793,10 +793,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,13 +816,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -844,7 +844,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -855,7 +855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -866,7 +866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -877,7 +877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -888,7 +888,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -910,7 +910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -921,7 +921,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -932,7 +932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -943,7 +943,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -954,7 +954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -965,7 +965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -976,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -987,7 +987,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -998,7 +998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1160,14 +1160,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1289,13 +1289,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1348,14 +1348,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1419,12 +1419,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1456,22 +1456,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1484,9 +1484,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,14 +1527,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,78 +1545,78 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -1631,13 +1631,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,67 +1648,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1722,13 +1722,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,67 +1739,67 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1813,7 +1813,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GovGrants_Product_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9263A4D9-CFF2-4369-85F8-1EC92B8CCA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -757,13 +757,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -785,7 +785,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -796,7 +796,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -816,13 +816,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -833,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -844,7 +844,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -855,7 +855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -866,7 +866,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -877,7 +877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -888,7 +888,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -910,7 +910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -921,7 +921,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -932,7 +932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -943,7 +943,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -954,7 +954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -965,7 +965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -976,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -987,7 +987,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -998,7 +998,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1160,14 +1160,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1289,13 +1289,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1348,14 +1348,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1419,12 +1419,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1456,22 +1456,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1484,9 +1484,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,14 +1527,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1631,13 +1631,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1722,13 +1722,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1813,7 +1813,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
